--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486697_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486697_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2406</v>
+        <v>6.6668</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8488</v>
+        <v>6.3246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3918</v>
+        <v>0.3421</v>
       </c>
       <c r="G2" t="n">
         <v>4.468</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6328</v>
+        <v>-1.2066</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0209</v>
+        <v>-0.5451</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6119</v>
+        <v>-0.6615</v>
       </c>
       <c r="V2" t="n">
         <v>2.8262</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5416</v>
+        <v>2.0202</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6491</v>
+        <v>3.0285</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1076</v>
+        <v>-1.0082</v>
       </c>
       <c r="G3" t="n">
         <v>0.3178</v>
@@ -688,13 +688,13 @@
         <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.4713</v>
+        <v>-1.9927</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2417</v>
+        <v>-0.8623</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2297</v>
+        <v>-1.1303</v>
       </c>
       <c r="V3" t="n">
         <v>1.1851</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2151</v>
+        <v>-0.2621</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3526</v>
+        <v>-0.0552</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5678</v>
+        <v>-0.2069</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4137</v>
+        <v>-0.2069</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6006</v>
+        <v>-0.2069</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1868</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8424</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.538</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3044</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2562</v>
+        <v>-0.2069</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1386</v>
+        <v>-0.2069</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1176</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7668</v>
+        <v>-0.0552</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1383</v>
+        <v>-0.0552</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2621</v>
+        <v>-0.2827</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0552</v>
+        <v>0.3596</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2069</v>
+        <v>-0.6423</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2069</v>
+        <v>-0.4137</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2069</v>
+        <v>-1.6006</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.1868</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.8424</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.3044</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2069</v>
+        <v>-2.2562</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2069</v>
+        <v>-2.1386</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.1176</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0552</v>
+        <v>-0.8343</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0552</v>
+        <v>-0.1313</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0486</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5242</v>
+        <v>0.6828</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5728</v>
+        <v>-1.6722</v>
       </c>
       <c r="G6" t="n">
         <v>0.4756</v>
@@ -922,13 +922,13 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3971</v>
+        <v>-0.3378</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2207</v>
+        <v>-0.0621</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1763</v>
+        <v>-0.2757</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5133</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4221</v>
+        <v>-1.3724</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9102</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5119</v>
+        <v>-0.4622</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0966</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3255</v>
+        <v>-0.2759</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5145</v>
+        <v>-1.4027</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9668</v>
+        <v>1.0289</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4813</v>
+        <v>-2.4317</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0857</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0426</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2763</v>
+        <v>-0.2141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7664</v>
+        <v>-0.7167</v>
       </c>
       <c r="V8" t="n">
         <v>0.6138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>J. VALDERREY PULIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5334</v>
+        <v>-1.8645</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9669</v>
+        <v>-0.2149</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5664</v>
+        <v>-1.6495</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6848</v>
+        <v>-2.274</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5514</v>
+        <v>-0.0698</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1334</v>
+        <v>-2.2041</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3298</v>
+        <v>-0.3071</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2077</v>
+        <v>0.8277</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-1.1348</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0146</v>
+        <v>-1.9668</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7591</v>
+        <v>-0.8975</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2555</v>
+        <v>-1.0693</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6288</v>
+        <v>-0.7723</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1383</v>
+        <v>-0.0004</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4906</v>
+        <v>-0.772</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1851</v>
+        <v>-0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1851</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VALDERREY PULIDO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3832</v>
+        <v>-1.9319</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4357</v>
+        <v>-1.1668</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9475</v>
+        <v>-0.7651</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.274</v>
+        <v>-0.6848</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0698</v>
+        <v>-0.5514</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2041</v>
+        <v>-0.1334</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3071</v>
+        <v>0.3298</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8277</v>
+        <v>0.2077</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1348</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9668</v>
+        <v>-1.0146</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8975</v>
+        <v>-0.7591</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0693</v>
+        <v>-0.2555</v>
       </c>
       <c r="P10" t="n">
+        <v>0.9654</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.1239</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.3169</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.291</v>
+        <v>-1.0274</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2211</v>
+        <v>-0.3382</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0699</v>
+        <v>-0.6892</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9421</v>
+        <v>-1.1851</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6702</v>
+        <v>-2.6206</v>
       </c>
       <c r="E11" t="n">
         <v>-1.5376</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1326</v>
+        <v>-1.083</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3447</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3255</v>
+        <v>-0.2759</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2623</v>
+        <v>-3.1106</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.647</v>
+        <v>-2.3711</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6153</v>
+        <v>-0.7395</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0867</v>
@@ -1390,13 +1390,13 @@
         <v>3.4754</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4067</v>
+        <v>-1.2549</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6625</v>
+        <v>-0.3866</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7441</v>
+        <v>-0.8683</v>
       </c>
       <c r="V12" t="n">
         <v>3.9687</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.529300000000001</v>
+        <v>-5.149899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.788899999999999</v>
+        <v>5.168600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.3183</v>
+        <v>-10.3185</v>
       </c>
       <c r="G13" t="n">
         <v>-6.9317</v>
@@ -1438,16 +1438,16 @@
         <v>-7.587299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6556999999999995</v>
+        <v>0.6557000000000004</v>
       </c>
       <c r="J13" t="n">
-        <v>9.767999999999999</v>
+        <v>9.768000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>6.557399999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.210600000000001</v>
+        <v>3.2106</v>
       </c>
       <c r="M13" t="n">
         <v>-16.6997</v>
@@ -1468,13 +1468,13 @@
         <v>17.3771</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.3433</v>
+        <v>-8.963899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.416399999999999</v>
+        <v>-3.0367</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.927000000000001</v>
+        <v>-5.926900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.9533</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.9057</v>
+        <v>8.6366</v>
       </c>
       <c r="E14" t="n">
-        <v>7.307</v>
+        <v>7.4104</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5987</v>
+        <v>1.2262</v>
       </c>
       <c r="G14" t="n">
         <v>5.1099</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3171</v>
+        <v>2.0481</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9097</v>
+        <v>1.0132</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4074</v>
+        <v>1.0349</v>
       </c>
       <c r="V14" t="n">
         <v>0.8995</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1196</v>
+        <v>2.7515</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1124</v>
+        <v>2.9527</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0072</v>
+        <v>-0.2012</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7227</v>
+        <v>2.9623</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6961</v>
+        <v>4.1312</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4188</v>
+        <v>-1.1688</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3059</v>
+        <v>5.1223</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1106</v>
+        <v>4.9595</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8047</v>
+        <v>0.1628</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0286</v>
+        <v>-2.1599</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4145</v>
+        <v>-0.8283</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6142</v>
+        <v>-1.3316</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R15" t="n">
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2285</v>
+        <v>1.0482</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7372</v>
+        <v>0.6341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4912</v>
+        <v>0.4141</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9169</v>
+        <v>2.3667</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3664</v>
+        <v>2.285</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4495</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9623</v>
+        <v>-0.7227</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1312</v>
+        <v>1.6961</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1688</v>
+        <v>-2.4188</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1223</v>
+        <v>1.3059</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9595</v>
+        <v>2.1106</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1628</v>
+        <v>-0.8047</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1599</v>
+        <v>-2.0286</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8283</v>
+        <v>-0.4145</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3316</v>
+        <v>-1.6142</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0892</v>
+        <v>-1.1585</v>
       </c>
       <c r="R16" t="n">
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2135</v>
+        <v>1.4756</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0477</v>
+        <v>0.9099</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1658</v>
+        <v>0.5657</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3759</v>
+        <v>1.6765</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6405</v>
+        <v>2.719</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2646</v>
+        <v>-1.0425</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6908</v>
+        <v>0.7044</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6904</v>
+        <v>-0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3812</v>
+        <v>0.7732</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8618</v>
+        <v>1.0296</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5874</v>
+        <v>0.4146</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7256</v>
+        <v>0.615</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5527</v>
+        <v>-0.3251</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.897</v>
+        <v>-0.4833</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.1582</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9895</v>
+        <v>0.8482</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8679</v>
+        <v>0.4617</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1216</v>
+        <v>0.3865</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7989</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3258</v>
+        <v>1.5505</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1816</v>
+        <v>1.4919</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1442</v>
+        <v>0.0586</v>
       </c>
       <c r="G18" t="n">
         <v>1.4406</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9544</v>
+        <v>1.1791</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2756</v>
+        <v>0.5858</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.5933</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8415</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.117</v>
+        <v>1.4618</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0828</v>
+        <v>0.1241</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1998</v>
+        <v>1.3377</v>
       </c>
       <c r="G19" t="n">
         <v>0.5653</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0275</v>
+        <v>0.3172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U19" t="n">
-        <v>0.138</v>
+        <v>0.2759</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6078</v>
+        <v>0.0825</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7882</v>
+        <v>1.9858</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1804</v>
+        <v>-1.9032</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7044</v>
+        <v>-0.6908</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0687</v>
+        <v>0.6904</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7732</v>
+        <v>-1.3812</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0296</v>
+        <v>0.8618</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4146</v>
+        <v>1.5874</v>
       </c>
       <c r="L20" t="n">
-        <v>0.615</v>
+        <v>-0.7256</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3251</v>
+        <v>-1.5527</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4833</v>
+        <v>-0.897</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1582</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2205</v>
+        <v>1.6961</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4691</v>
+        <v>1.2132</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2486</v>
+        <v>0.483</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>1.8415</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4554</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4497</v>
+        <v>-0.3215</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5614</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0111</v>
+        <v>-0.9863</v>
       </c>
       <c r="G21" t="n">
         <v>-0.218</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2317</v>
+        <v>-0.1035</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1213</v>
+        <v>-0.0965</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0015</v>
+        <v>-1.7208</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6628</v>
+        <v>-3.1268</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3387</v>
+        <v>1.406</v>
       </c>
       <c r="G22" t="n">
-        <v>1.51</v>
+        <v>0.8319</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3098</v>
+        <v>0.6963</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8198</v>
+        <v>0.1356</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1588</v>
+        <v>1.2328</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1027</v>
+        <v>1.1107</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2615</v>
+        <v>0.1221</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3513</v>
+        <v>-0.4009</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2071</v>
+        <v>-0.4145</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5583</v>
+        <v>0.0135</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8962</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8616</v>
+        <v>-4.0546</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6123</v>
+        <v>0.8069</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4688</v>
+        <v>0.3514</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1436</v>
+        <v>0.4554</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5712</v>
+        <v>-0.6565</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1634</v>
+        <v>-2.0207</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.644</v>
+        <v>-1.8697</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4805</v>
+        <v>-0.1511</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8319</v>
+        <v>1.51</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6963</v>
+        <v>-0.3098</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1356</v>
+        <v>1.8198</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2328</v>
+        <v>1.1588</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1107</v>
+        <v>-0.1027</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1221</v>
+        <v>1.2615</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4009</v>
+        <v>0.3513</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4145</v>
+        <v>-0.2071</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0135</v>
+        <v>0.5583</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7031</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0546</v>
+        <v>-3.8616</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3643</v>
+        <v>0.5931</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1657</v>
+        <v>0.2619</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5299</v>
+        <v>0.3312</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6565</v>
+        <v>0.5712</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6786</v>
+        <v>-2.1118</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3319</v>
+        <v>-0.8148</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3467</v>
+        <v>-1.297</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9394</v>
@@ -2326,13 +2326,13 @@
         <v>0.1931</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.353</v>
+        <v>0.2137</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2484</v>
+        <v>0.2687</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1047</v>
+        <v>-0.055</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6138</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5461</v>
+        <v>-5.1324</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9176</v>
+        <v>-3.504</v>
       </c>
       <c r="F25" t="n">
         <v>-1.6284</v>
@@ -2404,10 +2404,10 @@
         <v>0.5792</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4965</v>
+        <v>0.9102</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2208</v>
+        <v>0.1928</v>
       </c>
       <c r="U25" t="n">
         <v>0.7174</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.529400000000002</v>
+        <v>7.218899999999999</v>
       </c>
       <c r="E26" t="n">
         <v>10.3184</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.789000000000001</v>
+        <v>-3.0995</v>
       </c>
       <c r="G26" t="n">
         <v>6.931699999999999</v>
@@ -2452,7 +2452,7 @@
         <v>7.587300000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6553999999999998</v>
+        <v>-0.6554000000000002</v>
       </c>
       <c r="J26" t="n">
         <v>16.6999</v>
@@ -2461,10 +2461,10 @@
         <v>14.1448</v>
       </c>
       <c r="L26" t="n">
-        <v>2.5552</v>
+        <v>2.555200000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.767900000000001</v>
+        <v>-9.767899999999997</v>
       </c>
       <c r="N26" t="n">
         <v>-6.5575</v>
@@ -2473,7 +2473,7 @@
         <v>-3.2107</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.792399999999999</v>
+        <v>-5.792400000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.3771</v>
@@ -2482,13 +2482,13 @@
         <v>11.5845</v>
       </c>
       <c r="S26" t="n">
-        <v>10.3434</v>
+        <v>11.0329</v>
       </c>
       <c r="T26" t="n">
-        <v>5.927</v>
+        <v>5.927099999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.4164</v>
+        <v>5.1059</v>
       </c>
       <c r="V26" t="n">
         <v>-4.9533</v>
